--- a/docs/日志.xlsx
+++ b/docs/日志.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="7.6" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>工作日志表</t>
   </si>
@@ -59,6 +59,18 @@
   </si>
   <si>
     <t>需要根据实际情况选择合适的工具，并调整项目方案。</t>
+  </si>
+  <si>
+    <t>安装基础包文件，完成向量化和初步的智能体及记忆测试</t>
+  </si>
+  <si>
+    <t>在虚拟环境内完成了所有包文件安装，成功实现了智能体功能。</t>
+  </si>
+  <si>
+    <t>校园网连接hf镜像网站时速度较慢，推测可能是限速或大量同学同时使用的原因，需要挂梯子或者直接下载源文件。</t>
+  </si>
+  <si>
+    <t>要使用虚拟环境进行项目隔离，减少兼容冲突问题。</t>
   </si>
 </sst>
 </file>
@@ -1067,9 +1079,63 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="35.3636363636364" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="3" ht="52" customHeight="1" spans="1:2">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" ht="81" customHeight="1" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="158" customHeight="1" spans="1:2">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1" spans="1:2">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
